--- a/Mapping of Sustainability and Climate risk to Financial Impact Infracredit.xlsx
+++ b/Mapping of Sustainability and Climate risk to Financial Impact Infracredit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F83C4A34-E010-42D7-A7A0-9FA02C9DE277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69F48727-9245-41DA-AFFA-6D69D2F71188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{0DAF4852-E5D9-46DC-BFCD-64D48B52386C}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="386">
   <si>
     <t>Risk</t>
   </si>
@@ -2037,6 +2037,231 @@
   </si>
   <si>
     <t>Strong compliance framework supports sustainable operations and investor confidence.</t>
+  </si>
+  <si>
+    <t>Climate Risk Identified</t>
+  </si>
+  <si>
+    <t>New sustainability disclosure standards may require collection, verification, and reporting of emissions data</t>
+  </si>
+  <si>
+    <t>Additional costs will be incurred to collect, verify, and report ESG and emissions data</t>
+  </si>
+  <si>
+    <t>Better data improves risk assessment and strengthens investor confidence</t>
+  </si>
+  <si>
+    <t>Strong ESG reporting enhances access to funding and supports long-term credibility</t>
+  </si>
+  <si>
+    <t>Stricter Environmental Regulations</t>
+  </si>
+  <si>
+    <t>Adoption of low-carbon policies may affect client solvency and asset valuation</t>
+  </si>
+  <si>
+    <t>Clients may face higher costs, increasing the risk of default and potential losses</t>
+  </si>
+  <si>
+    <t>Portfolio gradually shifts toward more compliant and lower-risk sectors</t>
+  </si>
+  <si>
+    <t>Reduced exposure to high-risk sectors leads to more stable returns</t>
+  </si>
+  <si>
+    <t>Policy Shift Towards Renewable Energy</t>
+  </si>
+  <si>
+    <t>Incentives for renewable energy reduce viability of fossil-related investments</t>
+  </si>
+  <si>
+    <t>Fossil-related assets may lose value, leading to potential losses</t>
+  </si>
+  <si>
+    <t>Increased focus on renewable projects improves portfolio quality</t>
+  </si>
+  <si>
+    <t>Alignment with green energy supports stable and sustainable income</t>
+  </si>
+  <si>
+    <t>Stranded Assets</t>
+  </si>
+  <si>
+    <t>Clients’ assets may become obsolete due to transition to low-carbon technologies</t>
+  </si>
+  <si>
+    <t>Some client assets may become obsolete, increasing default risk and losses</t>
+  </si>
+  <si>
+    <t>Weak assets are gradually removed, improving overall portfolio strength</t>
+  </si>
+  <si>
+    <t>A cleaner portfolio reduces risk and supports long-term financial stability</t>
+  </si>
+  <si>
+    <t>Significant cost required to adapt operations and portfolio</t>
+  </si>
+  <si>
+    <t>Higher operational and investment costs reduce profitability</t>
+  </si>
+  <si>
+    <t>Efficiency improvements begin to offset these costs</t>
+  </si>
+  <si>
+    <t>Lower operating costs and better efficiency improve margins</t>
+  </si>
+  <si>
+    <t>Rapid pace of transition may outdate existing investments or models</t>
+  </si>
+  <si>
+    <t>Rapid changes may make existing investments less relevant or outdated</t>
+  </si>
+  <si>
+    <t>Updated systems and processes improve decision-making</t>
+  </si>
+  <si>
+    <t>Strong adaptability enhances long-term competitiveness</t>
+  </si>
+  <si>
+    <t>Technology Advancement</t>
+  </si>
+  <si>
+    <t>Investment in ESG systems, data infrastructure, and modelling tools</t>
+  </si>
+  <si>
+    <t>Investment in systems and tools increases costs</t>
+  </si>
+  <si>
+    <t>Improved systems enhance efficiency and risk monitoring</t>
+  </si>
+  <si>
+    <t>Strong digital capability supports better performance and cost control</t>
+  </si>
+  <si>
+    <t>Greenwashing Risk</t>
+  </si>
+  <si>
+    <t>Misrepresentation of sustainability practices may lead to regulatory and reputational risks</t>
+  </si>
+  <si>
+    <t>Risk of penalties and reputational damage if disclosures are misleading</t>
+  </si>
+  <si>
+    <t>Improved controls reduce exposure to regulatory risks</t>
+  </si>
+  <si>
+    <t>Strong credibility builds investor trust and supports growth</t>
+  </si>
+  <si>
+    <t>ESG &amp; Sustainability Expectations</t>
+  </si>
+  <si>
+    <t>Failure to meet stakeholder expectations on ESG disclosures and performance</t>
+  </si>
+  <si>
+    <t>Failure to meet expectations may reduce investor confidence</t>
+  </si>
+  <si>
+    <t>Improved ESG performance attracts more business opportunities</t>
+  </si>
+  <si>
+    <t>Strong ESG positioning supports long-term growth and reputation</t>
+  </si>
+  <si>
+    <t>Changing Customer Preferences</t>
+  </si>
+  <si>
+    <t>Shift toward ESG-aligned institutions reducing demand for non-aligned financing</t>
+  </si>
+  <si>
+    <t>Demand may reduce from clients prioritising ESG-compliant institutions</t>
+  </si>
+  <si>
+    <t>Shift toward sustainable financing creates new opportunities</t>
+  </si>
+  <si>
+    <t>ESG-aligned portfolio supports long-term growth and profitability</t>
+  </si>
+  <si>
+    <t>Physical Risk</t>
+  </si>
+  <si>
+    <t>Severe flooding affecting infrastructure assets and operations</t>
+  </si>
+  <si>
+    <t>Disruption to projects may increase defaults and financial losses</t>
+  </si>
+  <si>
+    <t>Improved project selection and risk management reduce exposure</t>
+  </si>
+  <si>
+    <t>Climate-resilient assets support stable performance</t>
+  </si>
+  <si>
+    <t>Extreme heat affecting infrastructure efficiency and operations</t>
+  </si>
+  <si>
+    <t>Increased costs and reduced efficiency of infrastructure</t>
+  </si>
+  <si>
+    <t>Adaptation measures improve operational performance</t>
+  </si>
+  <si>
+    <t>More efficient systems reduce long-term cost pressures</t>
+  </si>
+  <si>
+    <t>Disruption of infrastructure and logistics affecting project operations</t>
+  </si>
+  <si>
+    <t>Disruption increases risk and operational costs</t>
+  </si>
+  <si>
+    <t>Better planning reduces the impact of disruptions</t>
+  </si>
+  <si>
+    <t>More resilient infrastructure reduces long-term risks</t>
+  </si>
+  <si>
+    <t>Rising Temperature</t>
+  </si>
+  <si>
+    <t>Increased cooling demand for infrastructure and systems</t>
+  </si>
+  <si>
+    <t>Higher energy costs increase operational expenses</t>
+  </si>
+  <si>
+    <t>Efficiency improvements help manage rising costs</t>
+  </si>
+  <si>
+    <t>Lower energy intensity improves profitability</t>
+  </si>
+  <si>
+    <t>Sea-Level Rise</t>
+  </si>
+  <si>
+    <t>Increased flooding, corrosion, and infrastructure degradation</t>
+  </si>
+  <si>
+    <t>Increased exposure to coastal asset risks</t>
+  </si>
+  <si>
+    <t>Gradual reduction in high-risk exposures</t>
+  </si>
+  <si>
+    <t>Stronger portfolio positioning reduces long-term risk</t>
+  </si>
+  <si>
+    <t>Damage to infrastructure and disruption of operations</t>
+  </si>
+  <si>
+    <t>Damage increases financial risk and losses</t>
+  </si>
+  <si>
+    <t>Improved risk management reduces exposure</t>
+  </si>
+  <si>
+    <t>Resilient assets reduce long-term financial impact</t>
   </si>
 </sst>
 </file>
@@ -2676,93 +2901,6 @@
     <xf numFmtId="0" fontId="3" fillId="13" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2817,6 +2955,93 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3358,7 +3583,7 @@
       <c r="E6" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="88" t="s">
+      <c r="F6" s="59" t="s">
         <v>35</v>
       </c>
       <c r="G6" s="31" t="s">
@@ -3370,16 +3595,16 @@
     </row>
     <row r="7" spans="2:8" ht="116" x14ac:dyDescent="0.35">
       <c r="B7" s="82"/>
-      <c r="C7" s="68" t="s">
+      <c r="C7" s="85" t="s">
         <v>108</v>
       </c>
-      <c r="D7" s="90" t="s">
+      <c r="D7" s="61" t="s">
         <v>135</v>
       </c>
       <c r="E7" s="32" t="s">
         <v>149</v>
       </c>
-      <c r="F7" s="87" t="s">
+      <c r="F7" s="58" t="s">
         <v>197</v>
       </c>
       <c r="G7" s="33" t="s">
@@ -3389,7 +3614,7 @@
     </row>
     <row r="8" spans="2:8" ht="87" x14ac:dyDescent="0.35">
       <c r="B8" s="82"/>
-      <c r="C8" s="69"/>
+      <c r="C8" s="86"/>
       <c r="D8" s="16" t="s">
         <v>134</v>
       </c>
@@ -3406,7 +3631,7 @@
     </row>
     <row r="9" spans="2:8" ht="87" x14ac:dyDescent="0.35">
       <c r="B9" s="82"/>
-      <c r="C9" s="69"/>
+      <c r="C9" s="86"/>
       <c r="D9" s="16" t="s">
         <v>110</v>
       </c>
@@ -3423,8 +3648,8 @@
     </row>
     <row r="10" spans="2:8" ht="83.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B10" s="82"/>
-      <c r="C10" s="70"/>
-      <c r="D10" s="91" t="s">
+      <c r="C10" s="87"/>
+      <c r="D10" s="62" t="s">
         <v>20</v>
       </c>
       <c r="E10" s="36" t="s">
@@ -3440,33 +3665,33 @@
     </row>
     <row r="11" spans="2:8" ht="38" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="82"/>
-      <c r="C11" s="71" t="s">
+      <c r="C11" s="97" t="s">
         <v>103</v>
       </c>
-      <c r="D11" s="92" t="s">
+      <c r="D11" s="63" t="s">
         <v>151</v>
       </c>
       <c r="E11" s="43" t="s">
         <v>152</v>
       </c>
-      <c r="F11" s="85" t="s">
+      <c r="F11" s="56" t="s">
         <v>178</v>
       </c>
-      <c r="G11" s="85" t="s">
+      <c r="G11" s="56" t="s">
         <v>201</v>
       </c>
       <c r="H11" s="40"/>
     </row>
     <row r="12" spans="2:8" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B12" s="82"/>
-      <c r="C12" s="72"/>
-      <c r="D12" s="93" t="s">
+      <c r="C12" s="98"/>
+      <c r="D12" s="64" t="s">
         <v>202</v>
       </c>
       <c r="E12" s="36" t="s">
         <v>205</v>
       </c>
-      <c r="F12" s="86" t="s">
+      <c r="F12" s="57" t="s">
         <v>204</v>
       </c>
       <c r="G12" s="41" t="s">
@@ -3476,10 +3701,10 @@
     </row>
     <row r="13" spans="2:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B13" s="82"/>
-      <c r="C13" s="68" t="s">
+      <c r="C13" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="90" t="s">
+      <c r="D13" s="61" t="s">
         <v>22</v>
       </c>
       <c r="E13" s="43" t="s">
@@ -3495,7 +3720,7 @@
     </row>
     <row r="14" spans="2:8" ht="72.5" x14ac:dyDescent="0.35">
       <c r="B14" s="82"/>
-      <c r="C14" s="69"/>
+      <c r="C14" s="86"/>
       <c r="D14" s="16" t="s">
         <v>23</v>
       </c>
@@ -3512,7 +3737,7 @@
     </row>
     <row r="15" spans="2:8" ht="29" x14ac:dyDescent="0.35">
       <c r="B15" s="82"/>
-      <c r="C15" s="69"/>
+      <c r="C15" s="86"/>
       <c r="D15" s="16" t="s">
         <v>124</v>
       </c>
@@ -3529,8 +3754,8 @@
     </row>
     <row r="16" spans="2:8" ht="73" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B16" s="82"/>
-      <c r="C16" s="70"/>
-      <c r="D16" s="91" t="s">
+      <c r="C16" s="87"/>
+      <c r="D16" s="62" t="s">
         <v>24</v>
       </c>
       <c r="E16" s="36" t="s">
@@ -3546,10 +3771,10 @@
     </row>
     <row r="17" spans="2:8" ht="58" x14ac:dyDescent="0.35">
       <c r="B17" s="82"/>
-      <c r="C17" s="68" t="s">
+      <c r="C17" s="85" t="s">
         <v>125</v>
       </c>
-      <c r="D17" s="90" t="s">
+      <c r="D17" s="61" t="s">
         <v>154</v>
       </c>
       <c r="E17" s="43" t="s">
@@ -3565,7 +3790,7 @@
     </row>
     <row r="18" spans="2:8" ht="159.5" x14ac:dyDescent="0.35">
       <c r="B18" s="82"/>
-      <c r="C18" s="69"/>
+      <c r="C18" s="86"/>
       <c r="D18" s="16" t="s">
         <v>49</v>
       </c>
@@ -3582,8 +3807,8 @@
     </row>
     <row r="19" spans="2:8" ht="78" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B19" s="82"/>
-      <c r="C19" s="70"/>
-      <c r="D19" s="91" t="s">
+      <c r="C19" s="87"/>
+      <c r="D19" s="62" t="s">
         <v>25</v>
       </c>
       <c r="E19" s="36" t="s">
@@ -3599,10 +3824,10 @@
     </row>
     <row r="20" spans="2:8" ht="72.5" x14ac:dyDescent="0.35">
       <c r="B20" s="82"/>
-      <c r="C20" s="65" t="s">
+      <c r="C20" s="79" t="s">
         <v>16</v>
       </c>
-      <c r="D20" s="94" t="s">
+      <c r="D20" s="65" t="s">
         <v>101</v>
       </c>
       <c r="E20" s="43" t="s">
@@ -3618,7 +3843,7 @@
     </row>
     <row r="21" spans="2:8" ht="72.5" x14ac:dyDescent="0.35">
       <c r="B21" s="82"/>
-      <c r="C21" s="66"/>
+      <c r="C21" s="80"/>
       <c r="D21" s="16" t="s">
         <v>65</v>
       </c>
@@ -3635,7 +3860,7 @@
     </row>
     <row r="22" spans="2:8" ht="72.5" x14ac:dyDescent="0.35">
       <c r="B22" s="82"/>
-      <c r="C22" s="66"/>
+      <c r="C22" s="80"/>
       <c r="D22" s="16" t="s">
         <v>111</v>
       </c>
@@ -3652,8 +3877,8 @@
     </row>
     <row r="23" spans="2:8" ht="73" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B23" s="82"/>
-      <c r="C23" s="66"/>
-      <c r="D23" s="95" t="s">
+      <c r="C23" s="80"/>
+      <c r="D23" s="66" t="s">
         <v>213</v>
       </c>
       <c r="E23" s="3" t="s">
@@ -3669,16 +3894,16 @@
     </row>
     <row r="24" spans="2:8" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="82"/>
-      <c r="C24" s="59" t="s">
+      <c r="C24" s="99" t="s">
         <v>102</v>
       </c>
-      <c r="D24" s="96" t="s">
+      <c r="D24" s="67" t="s">
         <v>17</v>
       </c>
       <c r="E24" s="43" t="s">
         <v>158</v>
       </c>
-      <c r="F24" s="85" t="s">
+      <c r="F24" s="56" t="s">
         <v>184</v>
       </c>
       <c r="G24" s="39" t="s">
@@ -3688,14 +3913,14 @@
     </row>
     <row r="25" spans="2:8" ht="39.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="82"/>
-      <c r="C25" s="60"/>
-      <c r="D25" s="97" t="s">
+      <c r="C25" s="100"/>
+      <c r="D25" s="68" t="s">
         <v>18</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="F25" s="89" t="s">
+      <c r="F25" s="60" t="s">
         <v>91</v>
       </c>
       <c r="G25" s="1" t="s">
@@ -3705,27 +3930,27 @@
     </row>
     <row r="26" spans="2:8" ht="50.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B26" s="82"/>
-      <c r="C26" s="61"/>
-      <c r="D26" s="98" t="s">
+      <c r="C26" s="101"/>
+      <c r="D26" s="69" t="s">
         <v>19</v>
       </c>
       <c r="E26" s="36" t="s">
         <v>159</v>
       </c>
-      <c r="F26" s="86" t="s">
+      <c r="F26" s="57" t="s">
         <v>218</v>
       </c>
-      <c r="G26" s="86" t="s">
+      <c r="G26" s="57" t="s">
         <v>217</v>
       </c>
       <c r="H26" s="42"/>
     </row>
     <row r="27" spans="2:8" ht="72" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B27" s="82"/>
-      <c r="C27" s="65" t="s">
+      <c r="C27" s="79" t="s">
         <v>109</v>
       </c>
-      <c r="D27" s="90" t="s">
+      <c r="D27" s="61" t="s">
         <v>1</v>
       </c>
       <c r="E27" s="43" t="s">
@@ -3741,7 +3966,7 @@
     </row>
     <row r="28" spans="2:8" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B28" s="82"/>
-      <c r="C28" s="66"/>
+      <c r="C28" s="80"/>
       <c r="D28" s="16" t="s">
         <v>61</v>
       </c>
@@ -3758,7 +3983,7 @@
     </row>
     <row r="29" spans="2:8" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="82"/>
-      <c r="C29" s="66"/>
+      <c r="C29" s="80"/>
       <c r="D29" s="16" t="s">
         <v>63</v>
       </c>
@@ -3775,8 +4000,8 @@
     </row>
     <row r="30" spans="2:8" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B30" s="82"/>
-      <c r="C30" s="67"/>
-      <c r="D30" s="91" t="s">
+      <c r="C30" s="81"/>
+      <c r="D30" s="62" t="s">
         <v>2</v>
       </c>
       <c r="E30" s="36" t="s">
@@ -3792,50 +4017,50 @@
     </row>
     <row r="31" spans="2:8" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="82"/>
-      <c r="C31" s="59" t="s">
+      <c r="C31" s="99" t="s">
         <v>107</v>
       </c>
-      <c r="D31" s="99" t="s">
+      <c r="D31" s="70" t="s">
         <v>29</v>
       </c>
-      <c r="E31" s="85" t="s">
+      <c r="E31" s="56" t="s">
         <v>161</v>
       </c>
-      <c r="F31" s="85" t="s">
+      <c r="F31" s="56" t="s">
         <v>188</v>
       </c>
-      <c r="G31" s="85" t="s">
+      <c r="G31" s="56" t="s">
         <v>221</v>
       </c>
       <c r="H31" s="40"/>
     </row>
     <row r="32" spans="2:8" ht="38" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="82"/>
-      <c r="C32" s="60"/>
-      <c r="D32" s="97" t="s">
+      <c r="C32" s="100"/>
+      <c r="D32" s="68" t="s">
         <v>163</v>
       </c>
-      <c r="E32" s="89" t="s">
+      <c r="E32" s="60" t="s">
         <v>164</v>
       </c>
-      <c r="F32" s="89" t="s">
+      <c r="F32" s="60" t="s">
         <v>189</v>
       </c>
-      <c r="G32" s="89" t="s">
+      <c r="G32" s="60" t="s">
         <v>222</v>
       </c>
       <c r="H32" s="48"/>
     </row>
     <row r="33" spans="2:8" ht="31" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B33" s="82"/>
-      <c r="C33" s="60"/>
-      <c r="D33" s="97" t="s">
+      <c r="C33" s="100"/>
+      <c r="D33" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="E33" s="89" t="s">
+      <c r="E33" s="60" t="s">
         <v>162</v>
       </c>
-      <c r="F33" s="89" t="s">
+      <c r="F33" s="60" t="s">
         <v>190</v>
       </c>
       <c r="G33" s="1" t="s">
@@ -3845,27 +4070,27 @@
     </row>
     <row r="34" spans="2:8" ht="33.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B34" s="82"/>
-      <c r="C34" s="60"/>
-      <c r="D34" s="97" t="s">
+      <c r="C34" s="100"/>
+      <c r="D34" s="68" t="s">
         <v>30</v>
       </c>
-      <c r="E34" s="89" t="s">
+      <c r="E34" s="60" t="s">
         <v>165</v>
       </c>
-      <c r="F34" s="89" t="s">
+      <c r="F34" s="60" t="s">
         <v>189</v>
       </c>
-      <c r="G34" s="89" t="s">
+      <c r="G34" s="60" t="s">
         <v>224</v>
       </c>
       <c r="H34" s="48"/>
     </row>
     <row r="35" spans="2:8" ht="58" x14ac:dyDescent="0.35">
       <c r="B35" s="82"/>
-      <c r="C35" s="68" t="s">
+      <c r="C35" s="85" t="s">
         <v>57</v>
       </c>
-      <c r="D35" s="90" t="s">
+      <c r="D35" s="61" t="s">
         <v>29</v>
       </c>
       <c r="E35" s="43" t="s">
@@ -3881,7 +4106,7 @@
     </row>
     <row r="36" spans="2:8" ht="58" x14ac:dyDescent="0.35">
       <c r="B36" s="82"/>
-      <c r="C36" s="69"/>
+      <c r="C36" s="86"/>
       <c r="D36" s="16" t="s">
         <v>127</v>
       </c>
@@ -3896,9 +4121,9 @@
       </c>
       <c r="H36" s="35"/>
     </row>
-    <row r="37" spans="2:8" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:8" ht="58" x14ac:dyDescent="0.35">
       <c r="B37" s="82"/>
-      <c r="C37" s="69"/>
+      <c r="C37" s="86"/>
       <c r="D37" s="16" t="s">
         <v>128</v>
       </c>
@@ -3915,8 +4140,8 @@
     </row>
     <row r="38" spans="2:8" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B38" s="82"/>
-      <c r="C38" s="70"/>
-      <c r="D38" s="91" t="s">
+      <c r="C38" s="87"/>
+      <c r="D38" s="62" t="s">
         <v>30</v>
       </c>
       <c r="E38" s="36" t="s">
@@ -3932,10 +4157,10 @@
     </row>
     <row r="39" spans="2:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B39" s="82"/>
-      <c r="C39" s="56" t="s">
+      <c r="C39" s="102" t="s">
         <v>100</v>
       </c>
-      <c r="D39" s="90" t="s">
+      <c r="D39" s="61" t="s">
         <v>26</v>
       </c>
       <c r="E39" s="43" t="s">
@@ -3951,7 +4176,7 @@
     </row>
     <row r="40" spans="2:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B40" s="82"/>
-      <c r="C40" s="57"/>
+      <c r="C40" s="103"/>
       <c r="D40" s="16" t="s">
         <v>52</v>
       </c>
@@ -3968,7 +4193,7 @@
     </row>
     <row r="41" spans="2:8" ht="58" x14ac:dyDescent="0.35">
       <c r="B41" s="82"/>
-      <c r="C41" s="57"/>
+      <c r="C41" s="103"/>
       <c r="D41" s="16" t="s">
         <v>27</v>
       </c>
@@ -3985,8 +4210,8 @@
     </row>
     <row r="42" spans="2:8" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B42" s="82"/>
-      <c r="C42" s="58"/>
-      <c r="D42" s="91" t="s">
+      <c r="C42" s="104"/>
+      <c r="D42" s="62" t="s">
         <v>4</v>
       </c>
       <c r="E42" s="36" t="s">
@@ -4002,33 +4227,33 @@
     </row>
     <row r="43" spans="2:8" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B43" s="82"/>
-      <c r="C43" s="59" t="s">
+      <c r="C43" s="99" t="s">
         <v>130</v>
       </c>
-      <c r="D43" s="100" t="s">
+      <c r="D43" s="71" t="s">
         <v>104</v>
       </c>
-      <c r="E43" s="85" t="s">
+      <c r="E43" s="56" t="s">
         <v>166</v>
       </c>
-      <c r="F43" s="85" t="s">
+      <c r="F43" s="56" t="s">
         <v>191</v>
       </c>
-      <c r="G43" s="85" t="s">
+      <c r="G43" s="56" t="s">
         <v>228</v>
       </c>
       <c r="H43" s="40"/>
     </row>
     <row r="44" spans="2:8" ht="41.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B44" s="82"/>
-      <c r="C44" s="60"/>
-      <c r="D44" s="101" t="s">
+      <c r="C44" s="100"/>
+      <c r="D44" s="72" t="s">
         <v>105</v>
       </c>
-      <c r="E44" s="89" t="s">
+      <c r="E44" s="60" t="s">
         <v>174</v>
       </c>
-      <c r="F44" s="89" t="s">
+      <c r="F44" s="60" t="s">
         <v>188</v>
       </c>
       <c r="G44" s="1" t="s">
@@ -4038,14 +4263,14 @@
     </row>
     <row r="45" spans="2:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B45" s="82"/>
-      <c r="C45" s="61"/>
-      <c r="D45" s="98" t="s">
+      <c r="C45" s="101"/>
+      <c r="D45" s="69" t="s">
         <v>106</v>
       </c>
-      <c r="E45" s="86" t="s">
+      <c r="E45" s="57" t="s">
         <v>167</v>
       </c>
-      <c r="F45" s="86" t="s">
+      <c r="F45" s="57" t="s">
         <v>230</v>
       </c>
       <c r="G45" s="41" t="s">
@@ -4055,33 +4280,33 @@
     </row>
     <row r="46" spans="2:8" ht="38.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="82"/>
-      <c r="C46" s="62" t="s">
+      <c r="C46" s="105" t="s">
         <v>112</v>
       </c>
-      <c r="D46" s="102" t="s">
+      <c r="D46" s="73" t="s">
         <v>168</v>
       </c>
-      <c r="E46" s="85" t="s">
+      <c r="E46" s="56" t="s">
         <v>169</v>
       </c>
-      <c r="F46" s="85" t="s">
+      <c r="F46" s="56" t="s">
         <v>192</v>
       </c>
-      <c r="G46" s="85" t="s">
+      <c r="G46" s="56" t="s">
         <v>232</v>
       </c>
       <c r="H46" s="40"/>
     </row>
     <row r="47" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B47" s="82"/>
-      <c r="C47" s="63"/>
-      <c r="D47" s="103" t="s">
+      <c r="C47" s="106"/>
+      <c r="D47" s="74" t="s">
         <v>170</v>
       </c>
-      <c r="E47" s="89" t="s">
+      <c r="E47" s="60" t="s">
         <v>171</v>
       </c>
-      <c r="F47" s="89" t="s">
+      <c r="F47" s="60" t="s">
         <v>178</v>
       </c>
       <c r="G47" s="1" t="s">
@@ -4091,14 +4316,14 @@
     </row>
     <row r="48" spans="2:8" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B48" s="82"/>
-      <c r="C48" s="64"/>
-      <c r="D48" s="104" t="s">
+      <c r="C48" s="107"/>
+      <c r="D48" s="75" t="s">
         <v>172</v>
       </c>
-      <c r="E48" s="86" t="s">
+      <c r="E48" s="57" t="s">
         <v>173</v>
       </c>
-      <c r="F48" s="86" t="s">
+      <c r="F48" s="57" t="s">
         <v>177</v>
       </c>
       <c r="G48" s="41" t="s">
@@ -4108,10 +4333,10 @@
     </row>
     <row r="49" spans="2:8" ht="69" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="82"/>
-      <c r="C49" s="65" t="s">
+      <c r="C49" s="79" t="s">
         <v>7</v>
       </c>
-      <c r="D49" s="90" t="s">
+      <c r="D49" s="61" t="s">
         <v>8</v>
       </c>
       <c r="E49" s="43" t="s">
@@ -4127,7 +4352,7 @@
     </row>
     <row r="50" spans="2:8" ht="96.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B50" s="82"/>
-      <c r="C50" s="66"/>
+      <c r="C50" s="80"/>
       <c r="D50" s="16" t="s">
         <v>9</v>
       </c>
@@ -4144,7 +4369,7 @@
     </row>
     <row r="51" spans="2:8" ht="54.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="82"/>
-      <c r="C51" s="66"/>
+      <c r="C51" s="80"/>
       <c r="D51" s="16" t="s">
         <v>10</v>
       </c>
@@ -4161,7 +4386,7 @@
     </row>
     <row r="52" spans="2:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B52" s="82"/>
-      <c r="C52" s="66"/>
+      <c r="C52" s="80"/>
       <c r="D52" s="16" t="s">
         <v>11</v>
       </c>
@@ -4178,8 +4403,8 @@
     </row>
     <row r="53" spans="2:8" ht="89" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B53" s="82"/>
-      <c r="C53" s="67"/>
-      <c r="D53" s="91" t="s">
+      <c r="C53" s="81"/>
+      <c r="D53" s="62" t="s">
         <v>12</v>
       </c>
       <c r="E53" s="36" t="s">
@@ -4195,10 +4420,10 @@
     </row>
     <row r="54" spans="2:8" ht="163" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B54" s="82"/>
-      <c r="C54" s="65" t="s">
+      <c r="C54" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="D54" s="90" t="s">
+      <c r="D54" s="61" t="s">
         <v>14</v>
       </c>
       <c r="E54" s="43" t="s">
@@ -4214,8 +4439,8 @@
     </row>
     <row r="55" spans="2:8" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B55" s="82"/>
-      <c r="C55" s="67"/>
-      <c r="D55" s="91" t="s">
+      <c r="C55" s="81"/>
+      <c r="D55" s="62" t="s">
         <v>15</v>
       </c>
       <c r="E55" s="36" t="s">
@@ -4234,7 +4459,7 @@
       <c r="C56" s="83" t="s">
         <v>6</v>
       </c>
-      <c r="D56" s="90" t="s">
+      <c r="D56" s="61" t="s">
         <v>54</v>
       </c>
       <c r="E56" s="43" t="s">
@@ -4251,7 +4476,7 @@
     <row r="57" spans="2:8" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B57" s="82"/>
       <c r="C57" s="84"/>
-      <c r="D57" s="91" t="s">
+      <c r="D57" s="62" t="s">
         <v>28</v>
       </c>
       <c r="E57" s="36" t="s">
@@ -4272,7 +4497,7 @@
       <c r="H58" s="27"/>
     </row>
     <row r="59" spans="2:8" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B59" s="75" t="s">
+      <c r="B59" s="90" t="s">
         <v>31</v>
       </c>
       <c r="C59" s="7"/>
@@ -4280,223 +4505,223 @@
       <c r="H59" s="27"/>
     </row>
     <row r="60" spans="2:8" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B60" s="75"/>
+      <c r="B60" s="90"/>
       <c r="C60" s="7"/>
       <c r="G60" s="27"/>
       <c r="H60" s="27"/>
     </row>
     <row r="61" spans="2:8" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B61" s="75"/>
+      <c r="B61" s="90"/>
       <c r="C61" s="7"/>
       <c r="G61" s="27"/>
       <c r="H61" s="27"/>
     </row>
     <row r="62" spans="2:8" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B62" s="75"/>
+      <c r="B62" s="90"/>
       <c r="C62" s="7"/>
     </row>
     <row r="63" spans="2:8" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B63" s="75"/>
+      <c r="B63" s="90"/>
       <c r="C63" s="7"/>
     </row>
     <row r="64" spans="2:8" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B64" s="75"/>
+      <c r="B64" s="90"/>
       <c r="C64" s="7"/>
     </row>
     <row r="65" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B65" s="75"/>
+      <c r="B65" s="90"/>
       <c r="C65" s="7"/>
     </row>
     <row r="66" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B66" s="75"/>
+      <c r="B66" s="90"/>
       <c r="C66" s="7"/>
     </row>
     <row r="67" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="75"/>
+      <c r="B67" s="90"/>
       <c r="C67" s="7"/>
     </row>
     <row r="68" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B68" s="75"/>
+      <c r="B68" s="90"/>
       <c r="C68" s="7"/>
     </row>
     <row r="69" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="75"/>
+      <c r="B69" s="90"/>
       <c r="C69" s="7"/>
     </row>
     <row r="70" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="75"/>
+      <c r="B70" s="90"/>
       <c r="C70" s="7"/>
     </row>
     <row r="71" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B71" s="75"/>
+      <c r="B71" s="90"/>
       <c r="C71" s="7"/>
     </row>
     <row r="72" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="75"/>
+      <c r="B72" s="90"/>
       <c r="C72" s="7"/>
     </row>
     <row r="73" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="75"/>
+      <c r="B73" s="90"/>
       <c r="C73" s="7"/>
     </row>
     <row r="74" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="75"/>
+      <c r="B74" s="90"/>
       <c r="C74" s="7"/>
     </row>
     <row r="75" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="75"/>
+      <c r="B75" s="90"/>
       <c r="C75" s="7"/>
     </row>
     <row r="76" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="75"/>
+      <c r="B76" s="90"/>
       <c r="C76" s="7"/>
     </row>
     <row r="77" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B77" s="75"/>
+      <c r="B77" s="90"/>
       <c r="C77" s="7"/>
     </row>
     <row r="78" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B78" s="75"/>
+      <c r="B78" s="90"/>
       <c r="C78" s="7"/>
     </row>
     <row r="79" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B79" s="75"/>
+      <c r="B79" s="90"/>
       <c r="C79" s="7"/>
     </row>
     <row r="80" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B80" s="75"/>
+      <c r="B80" s="90"/>
       <c r="C80" s="7"/>
     </row>
     <row r="81" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B81" s="75"/>
+      <c r="B81" s="90"/>
       <c r="C81" s="7"/>
     </row>
     <row r="82" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B82" s="75"/>
+      <c r="B82" s="90"/>
       <c r="C82" s="7"/>
     </row>
     <row r="83" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B83" s="75"/>
+      <c r="B83" s="90"/>
       <c r="C83" s="7"/>
     </row>
     <row r="84" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B84" s="75"/>
+      <c r="B84" s="90"/>
       <c r="C84" s="7"/>
     </row>
     <row r="85" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="75"/>
+      <c r="B85" s="90"/>
       <c r="C85" s="7"/>
     </row>
     <row r="86" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B86" s="75"/>
+      <c r="B86" s="90"/>
       <c r="C86" s="7"/>
     </row>
     <row r="87" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B87" s="75"/>
+      <c r="B87" s="90"/>
       <c r="C87" s="7"/>
     </row>
     <row r="88" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B88" s="75"/>
+      <c r="B88" s="90"/>
       <c r="C88" s="7"/>
     </row>
     <row r="89" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B89" s="75"/>
+      <c r="B89" s="90"/>
       <c r="C89" s="7"/>
     </row>
     <row r="90" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B90" s="75"/>
+      <c r="B90" s="90"/>
       <c r="C90" s="7"/>
     </row>
     <row r="91" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B91" s="75"/>
+      <c r="B91" s="90"/>
       <c r="C91" s="7"/>
     </row>
     <row r="92" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B92" s="75"/>
+      <c r="B92" s="90"/>
       <c r="C92" s="7"/>
     </row>
     <row r="93" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B93" s="75"/>
+      <c r="B93" s="90"/>
       <c r="C93" s="7"/>
     </row>
     <row r="94" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B94" s="75"/>
+      <c r="B94" s="90"/>
       <c r="C94" s="7"/>
     </row>
     <row r="95" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B95" s="75"/>
+      <c r="B95" s="90"/>
       <c r="C95" s="7"/>
     </row>
     <row r="96" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B96" s="75"/>
+      <c r="B96" s="90"/>
       <c r="C96" s="7"/>
     </row>
     <row r="97" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B97" s="75"/>
+      <c r="B97" s="90"/>
       <c r="C97" s="7"/>
     </row>
     <row r="98" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="75"/>
+      <c r="B98" s="90"/>
       <c r="C98" s="7"/>
     </row>
     <row r="99" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B99" s="75"/>
+      <c r="B99" s="90"/>
       <c r="C99" s="7"/>
     </row>
     <row r="100" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B100" s="75"/>
+      <c r="B100" s="90"/>
       <c r="C100" s="7"/>
     </row>
     <row r="101" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B101" s="75"/>
+      <c r="B101" s="90"/>
       <c r="C101" s="7"/>
     </row>
     <row r="102" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B102" s="75"/>
+      <c r="B102" s="90"/>
       <c r="C102" s="7"/>
     </row>
     <row r="103" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B103" s="75"/>
+      <c r="B103" s="90"/>
       <c r="C103" s="7"/>
     </row>
     <row r="104" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="75"/>
+      <c r="B104" s="90"/>
       <c r="C104" s="7"/>
     </row>
     <row r="105" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B105" s="75"/>
+      <c r="B105" s="90"/>
       <c r="C105" s="7"/>
     </row>
     <row r="106" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B106" s="75"/>
+      <c r="B106" s="90"/>
       <c r="C106" s="7"/>
     </row>
     <row r="107" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B107" s="75"/>
+      <c r="B107" s="90"/>
       <c r="C107" s="7"/>
     </row>
     <row r="108" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B108" s="75"/>
+      <c r="B108" s="90"/>
       <c r="C108" s="7"/>
     </row>
     <row r="109" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B109" s="75"/>
+      <c r="B109" s="90"/>
       <c r="C109" s="7"/>
     </row>
     <row r="110" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B110" s="75"/>
+      <c r="B110" s="90"/>
       <c r="C110" s="7"/>
     </row>
     <row r="111" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B111" s="75"/>
+      <c r="B111" s="90"/>
       <c r="C111" s="7"/>
     </row>
     <row r="112" spans="2:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B112" s="75"/>
+      <c r="B112" s="90"/>
       <c r="C112" s="7"/>
     </row>
     <row r="113" spans="2:8" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B113" s="75"/>
+      <c r="B113" s="90"/>
       <c r="C113" s="7"/>
     </row>
     <row r="118" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -4524,10 +4749,10 @@
       </c>
     </row>
     <row r="120" spans="2:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="B120" s="76" t="s">
+      <c r="B120" s="91" t="s">
         <v>5</v>
       </c>
-      <c r="C120" s="78" t="s">
+      <c r="C120" s="93" t="s">
         <v>72</v>
       </c>
       <c r="D120" s="11" t="s">
@@ -4541,8 +4766,8 @@
       <c r="H120" s="25"/>
     </row>
     <row r="121" spans="2:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="B121" s="76"/>
-      <c r="C121" s="78"/>
+      <c r="B121" s="91"/>
+      <c r="C121" s="93"/>
       <c r="D121" s="53" t="s">
         <v>142</v>
       </c>
@@ -4554,8 +4779,8 @@
       <c r="H121" s="25"/>
     </row>
     <row r="122" spans="2:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="B122" s="76"/>
-      <c r="C122" s="78"/>
+      <c r="B122" s="91"/>
+      <c r="C122" s="93"/>
       <c r="D122" s="12" t="s">
         <v>74</v>
       </c>
@@ -4567,8 +4792,8 @@
       <c r="H122" s="25"/>
     </row>
     <row r="123" spans="2:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="B123" s="76"/>
-      <c r="C123" s="79" t="s">
+      <c r="B123" s="91"/>
+      <c r="C123" s="94" t="s">
         <v>76</v>
       </c>
       <c r="D123" s="55" t="s">
@@ -4582,8 +4807,8 @@
       <c r="H123" s="25"/>
     </row>
     <row r="124" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B124" s="76"/>
-      <c r="C124" s="79"/>
+      <c r="B124" s="91"/>
+      <c r="C124" s="94"/>
       <c r="D124" s="55" t="s">
         <v>147</v>
       </c>
@@ -4593,8 +4818,8 @@
       <c r="H124" s="25"/>
     </row>
     <row r="125" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B125" s="76"/>
-      <c r="C125" s="79"/>
+      <c r="B125" s="91"/>
+      <c r="C125" s="94"/>
       <c r="D125" s="55" t="s">
         <v>148</v>
       </c>
@@ -4604,8 +4829,8 @@
       <c r="H125" s="25"/>
     </row>
     <row r="126" spans="2:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="B126" s="76"/>
-      <c r="C126" s="79"/>
+      <c r="B126" s="91"/>
+      <c r="C126" s="94"/>
       <c r="D126" s="55" t="s">
         <v>143</v>
       </c>
@@ -4617,8 +4842,8 @@
       <c r="H126" s="25"/>
     </row>
     <row r="127" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B127" s="76"/>
-      <c r="C127" s="80" t="s">
+      <c r="B127" s="91"/>
+      <c r="C127" s="95" t="s">
         <v>79</v>
       </c>
       <c r="D127" s="52" t="s">
@@ -4630,8 +4855,8 @@
       <c r="H127" s="25"/>
     </row>
     <row r="128" spans="2:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="B128" s="76"/>
-      <c r="C128" s="81"/>
+      <c r="B128" s="91"/>
+      <c r="C128" s="96"/>
       <c r="D128" s="52" t="s">
         <v>144</v>
       </c>
@@ -4643,7 +4868,7 @@
       <c r="H128" s="25"/>
     </row>
     <row r="129" spans="2:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="B129" s="77"/>
+      <c r="B129" s="92"/>
       <c r="C129" s="28"/>
       <c r="D129" s="54" t="s">
         <v>113</v>
@@ -4665,10 +4890,10 @@
       <c r="H130" s="21"/>
     </row>
     <row r="131" spans="2:8" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="B131" s="73" t="s">
+      <c r="B131" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C131" s="74" t="s">
+      <c r="C131" s="89" t="s">
         <v>82</v>
       </c>
       <c r="D131" s="52" t="s">
@@ -4682,8 +4907,8 @@
       <c r="H131" s="25"/>
     </row>
     <row r="132" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B132" s="73"/>
-      <c r="C132" s="74"/>
+      <c r="B132" s="88"/>
+      <c r="C132" s="89"/>
       <c r="D132" s="3" t="s">
         <v>140</v>
       </c>
@@ -4693,8 +4918,8 @@
       <c r="H132" s="25"/>
     </row>
     <row r="133" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B133" s="73"/>
-      <c r="C133" s="74"/>
+      <c r="B133" s="88"/>
+      <c r="C133" s="89"/>
       <c r="D133" s="3" t="s">
         <v>141</v>
       </c>
@@ -4704,8 +4929,8 @@
       <c r="H133" s="25"/>
     </row>
     <row r="134" spans="2:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="B134" s="73"/>
-      <c r="C134" s="74"/>
+      <c r="B134" s="88"/>
+      <c r="C134" s="89"/>
       <c r="D134" s="52" t="s">
         <v>138</v>
       </c>
@@ -4717,8 +4942,8 @@
       <c r="H134" s="25"/>
     </row>
     <row r="135" spans="2:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="B135" s="73"/>
-      <c r="C135" s="74" t="s">
+      <c r="B135" s="88"/>
+      <c r="C135" s="89" t="s">
         <v>84</v>
       </c>
       <c r="D135" s="52" t="s">
@@ -4732,8 +4957,8 @@
       <c r="H135" s="25"/>
     </row>
     <row r="136" spans="2:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="B136" s="73"/>
-      <c r="C136" s="74"/>
+      <c r="B136" s="88"/>
+      <c r="C136" s="89"/>
       <c r="D136" s="52" t="s">
         <v>86</v>
       </c>
@@ -4745,8 +4970,8 @@
       <c r="H136" s="25"/>
     </row>
     <row r="137" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B137" s="73"/>
-      <c r="C137" s="74"/>
+      <c r="B137" s="88"/>
+      <c r="C137" s="89"/>
       <c r="D137" s="52" t="s">
         <v>139</v>
       </c>
@@ -4760,11 +4985,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="C49:C53"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="B6:B57"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="C7:C10"/>
     <mergeCell ref="B131:B137"/>
     <mergeCell ref="C131:C134"/>
     <mergeCell ref="C135:C137"/>
@@ -4773,6 +4993,11 @@
     <mergeCell ref="C120:C122"/>
     <mergeCell ref="C123:C126"/>
     <mergeCell ref="C127:C128"/>
+    <mergeCell ref="C49:C53"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="B6:B57"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="C7:C10"/>
     <mergeCell ref="C11:C12"/>
     <mergeCell ref="C13:C16"/>
     <mergeCell ref="C17:C19"/>
@@ -4797,29 +5022,29 @@
   <conditionalFormatting sqref="C17:C18">
     <cfRule type="duplicateValues" dxfId="8" priority="10"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C20:C22">
+    <cfRule type="duplicateValues" dxfId="7" priority="47"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C24">
-    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C27:C29">
+    <cfRule type="duplicateValues" dxfId="5" priority="48"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C31:C32">
+    <cfRule type="duplicateValues" dxfId="4" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C35:C37">
-    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C39">
-    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43:C44">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C56 C54 C49">
-    <cfRule type="duplicateValues" dxfId="3" priority="30"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C20:C22">
-    <cfRule type="duplicateValues" dxfId="2" priority="47"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C27:C29">
-    <cfRule type="duplicateValues" dxfId="1" priority="48"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C31:C32">
-    <cfRule type="duplicateValues" dxfId="0" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="15" orientation="portrait" r:id="rId1"/>
@@ -4829,262 +5054,574 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8038B8B-F9A2-404F-93D2-7826D89607B7}">
-  <dimension ref="C3:G17"/>
+  <dimension ref="C3:O20"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="3" spans="3:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="C3" s="105" t="s">
+    <row r="3" spans="3:15" ht="29" x14ac:dyDescent="0.35">
+      <c r="C3" s="76" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="105" t="s">
+      <c r="D3" s="76" t="s">
         <v>243</v>
       </c>
-      <c r="E3" s="105" t="s">
+      <c r="E3" s="76" t="s">
         <v>244</v>
       </c>
-      <c r="F3" s="105" t="s">
+      <c r="F3" s="76" t="s">
         <v>245</v>
       </c>
-      <c r="G3" s="105" t="s">
+      <c r="G3" s="76" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="4" spans="3:7" ht="203" x14ac:dyDescent="0.35">
-      <c r="C4" s="107" t="s">
+    <row r="4" spans="3:15" ht="203" x14ac:dyDescent="0.35">
+      <c r="C4" s="78" t="s">
         <v>247</v>
       </c>
-      <c r="D4" s="106" t="s">
+      <c r="D4" s="77" t="s">
         <v>248</v>
       </c>
-      <c r="E4" s="106" t="s">
+      <c r="E4" s="77" t="s">
         <v>249</v>
       </c>
-      <c r="F4" s="106" t="s">
+      <c r="F4" s="77" t="s">
         <v>250</v>
       </c>
-      <c r="G4" s="106" t="s">
+      <c r="G4" s="77" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="5" spans="3:7" ht="188.5" x14ac:dyDescent="0.35">
-      <c r="C5" s="107" t="s">
+      <c r="J4" s="76" t="s">
+        <v>67</v>
+      </c>
+      <c r="K4" s="76" t="s">
+        <v>311</v>
+      </c>
+      <c r="L4" s="76" t="s">
+        <v>243</v>
+      </c>
+      <c r="M4" s="76" t="s">
+        <v>244</v>
+      </c>
+      <c r="N4" s="76" t="s">
+        <v>245</v>
+      </c>
+      <c r="O4" s="76" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="5" spans="3:15" ht="232" x14ac:dyDescent="0.35">
+      <c r="C5" s="78" t="s">
         <v>252</v>
       </c>
-      <c r="D5" s="106" t="s">
+      <c r="D5" s="77" t="s">
         <v>253</v>
       </c>
-      <c r="E5" s="106" t="s">
+      <c r="E5" s="77" t="s">
         <v>254</v>
       </c>
-      <c r="F5" s="106" t="s">
+      <c r="F5" s="77" t="s">
         <v>255</v>
       </c>
-      <c r="G5" s="106" t="s">
+      <c r="G5" s="77" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="6" spans="3:7" ht="159.5" x14ac:dyDescent="0.35">
-      <c r="C6" s="107" t="s">
+      <c r="J5" s="78" t="s">
+        <v>5</v>
+      </c>
+      <c r="K5" s="77" t="s">
+        <v>73</v>
+      </c>
+      <c r="L5" s="77" t="s">
+        <v>312</v>
+      </c>
+      <c r="M5" s="77" t="s">
+        <v>313</v>
+      </c>
+      <c r="N5" s="77" t="s">
+        <v>314</v>
+      </c>
+      <c r="O5" s="77" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="6" spans="3:15" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="C6" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="106" t="s">
+      <c r="D6" s="77" t="s">
         <v>257</v>
       </c>
-      <c r="E6" s="106" t="s">
+      <c r="E6" s="77" t="s">
         <v>258</v>
       </c>
-      <c r="F6" s="106" t="s">
+      <c r="F6" s="77" t="s">
         <v>259</v>
       </c>
-      <c r="G6" s="106" t="s">
+      <c r="G6" s="77" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="7" spans="3:7" ht="159.5" x14ac:dyDescent="0.35">
-      <c r="C7" s="107" t="s">
+      <c r="J6" s="78" t="s">
+        <v>5</v>
+      </c>
+      <c r="K6" s="77" t="s">
+        <v>316</v>
+      </c>
+      <c r="L6" s="77" t="s">
+        <v>317</v>
+      </c>
+      <c r="M6" s="77" t="s">
+        <v>318</v>
+      </c>
+      <c r="N6" s="77" t="s">
+        <v>319</v>
+      </c>
+      <c r="O6" s="77" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="7" spans="3:15" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="C7" s="78" t="s">
         <v>261</v>
       </c>
-      <c r="D7" s="106" t="s">
+      <c r="D7" s="77" t="s">
         <v>262</v>
       </c>
-      <c r="E7" s="106" t="s">
+      <c r="E7" s="77" t="s">
         <v>263</v>
       </c>
-      <c r="F7" s="106" t="s">
+      <c r="F7" s="77" t="s">
         <v>264</v>
       </c>
-      <c r="G7" s="106" t="s">
+      <c r="G7" s="77" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="8" spans="3:7" ht="159.5" x14ac:dyDescent="0.35">
-      <c r="C8" s="107" t="s">
+      <c r="J7" s="78" t="s">
+        <v>5</v>
+      </c>
+      <c r="K7" s="77" t="s">
+        <v>321</v>
+      </c>
+      <c r="L7" s="77" t="s">
+        <v>322</v>
+      </c>
+      <c r="M7" s="77" t="s">
+        <v>323</v>
+      </c>
+      <c r="N7" s="77" t="s">
+        <v>324</v>
+      </c>
+      <c r="O7" s="77" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="8" spans="3:15" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="C8" s="78" t="s">
         <v>266</v>
       </c>
-      <c r="D8" s="106" t="s">
+      <c r="D8" s="77" t="s">
         <v>267</v>
       </c>
-      <c r="E8" s="106" t="s">
+      <c r="E8" s="77" t="s">
         <v>268</v>
       </c>
-      <c r="F8" s="106" t="s">
+      <c r="F8" s="77" t="s">
         <v>269</v>
       </c>
-      <c r="G8" s="106" t="s">
+      <c r="G8" s="77" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="9" spans="3:7" ht="145" x14ac:dyDescent="0.35">
-      <c r="C9" s="107" t="s">
+      <c r="J8" s="78" t="s">
+        <v>5</v>
+      </c>
+      <c r="K8" s="77" t="s">
+        <v>326</v>
+      </c>
+      <c r="L8" s="77" t="s">
+        <v>327</v>
+      </c>
+      <c r="M8" s="77" t="s">
+        <v>328</v>
+      </c>
+      <c r="N8" s="77" t="s">
+        <v>329</v>
+      </c>
+      <c r="O8" s="77" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="9" spans="3:15" ht="145" x14ac:dyDescent="0.35">
+      <c r="C9" s="78" t="s">
         <v>102</v>
       </c>
-      <c r="D9" s="106" t="s">
+      <c r="D9" s="77" t="s">
         <v>271</v>
       </c>
-      <c r="E9" s="106" t="s">
+      <c r="E9" s="77" t="s">
         <v>272</v>
       </c>
-      <c r="F9" s="106" t="s">
+      <c r="F9" s="77" t="s">
         <v>273</v>
       </c>
-      <c r="G9" s="106" t="s">
+      <c r="G9" s="77" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="10" spans="3:7" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="C10" s="107" t="s">
+      <c r="J9" s="78" t="s">
+        <v>5</v>
+      </c>
+      <c r="K9" s="77" t="s">
+        <v>147</v>
+      </c>
+      <c r="L9" s="77" t="s">
+        <v>331</v>
+      </c>
+      <c r="M9" s="77" t="s">
+        <v>332</v>
+      </c>
+      <c r="N9" s="77" t="s">
+        <v>333</v>
+      </c>
+      <c r="O9" s="77" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="10" spans="3:15" ht="145" x14ac:dyDescent="0.35">
+      <c r="C10" s="78" t="s">
         <v>109</v>
       </c>
-      <c r="D10" s="106" t="s">
+      <c r="D10" s="77" t="s">
         <v>275</v>
       </c>
-      <c r="E10" s="106" t="s">
+      <c r="E10" s="77" t="s">
         <v>276</v>
       </c>
-      <c r="F10" s="106" t="s">
+      <c r="F10" s="77" t="s">
         <v>277</v>
       </c>
-      <c r="G10" s="106" t="s">
+      <c r="G10" s="77" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="11" spans="3:7" ht="145" x14ac:dyDescent="0.35">
-      <c r="C11" s="107" t="s">
+      <c r="J10" s="78" t="s">
+        <v>5</v>
+      </c>
+      <c r="K10" s="77" t="s">
+        <v>148</v>
+      </c>
+      <c r="L10" s="77" t="s">
+        <v>335</v>
+      </c>
+      <c r="M10" s="77" t="s">
+        <v>336</v>
+      </c>
+      <c r="N10" s="77" t="s">
+        <v>337</v>
+      </c>
+      <c r="O10" s="77" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="11" spans="3:15" ht="145" x14ac:dyDescent="0.35">
+      <c r="C11" s="78" t="s">
         <v>107</v>
       </c>
-      <c r="D11" s="106" t="s">
+      <c r="D11" s="77" t="s">
         <v>279</v>
       </c>
-      <c r="E11" s="106" t="s">
+      <c r="E11" s="77" t="s">
         <v>280</v>
       </c>
-      <c r="F11" s="106" t="s">
+      <c r="F11" s="77" t="s">
         <v>281</v>
       </c>
-      <c r="G11" s="106" t="s">
+      <c r="G11" s="77" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="12" spans="3:7" ht="145" x14ac:dyDescent="0.35">
-      <c r="C12" s="107" t="s">
+      <c r="J11" s="78" t="s">
+        <v>5</v>
+      </c>
+      <c r="K11" s="77" t="s">
+        <v>339</v>
+      </c>
+      <c r="L11" s="77" t="s">
+        <v>340</v>
+      </c>
+      <c r="M11" s="77" t="s">
+        <v>341</v>
+      </c>
+      <c r="N11" s="77" t="s">
+        <v>342</v>
+      </c>
+      <c r="O11" s="77" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="12" spans="3:15" ht="174" x14ac:dyDescent="0.35">
+      <c r="C12" s="78" t="s">
         <v>283</v>
       </c>
-      <c r="D12" s="106" t="s">
+      <c r="D12" s="77" t="s">
         <v>284</v>
       </c>
-      <c r="E12" s="106" t="s">
+      <c r="E12" s="77" t="s">
         <v>285</v>
       </c>
-      <c r="F12" s="106" t="s">
+      <c r="F12" s="77" t="s">
         <v>286</v>
       </c>
-      <c r="G12" s="106" t="s">
+      <c r="G12" s="77" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="13" spans="3:7" ht="145" x14ac:dyDescent="0.35">
-      <c r="C13" s="107" t="s">
+      <c r="J12" s="78" t="s">
+        <v>5</v>
+      </c>
+      <c r="K12" s="77" t="s">
+        <v>344</v>
+      </c>
+      <c r="L12" s="77" t="s">
+        <v>345</v>
+      </c>
+      <c r="M12" s="77" t="s">
+        <v>346</v>
+      </c>
+      <c r="N12" s="77" t="s">
+        <v>347</v>
+      </c>
+      <c r="O12" s="77" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="13" spans="3:15" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="C13" s="78" t="s">
         <v>288</v>
       </c>
-      <c r="D13" s="106" t="s">
+      <c r="D13" s="77" t="s">
         <v>289</v>
       </c>
-      <c r="E13" s="106" t="s">
+      <c r="E13" s="77" t="s">
         <v>290</v>
       </c>
-      <c r="F13" s="106" t="s">
+      <c r="F13" s="77" t="s">
         <v>291</v>
       </c>
-      <c r="G13" s="106" t="s">
+      <c r="G13" s="77" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="14" spans="3:7" ht="159.5" x14ac:dyDescent="0.35">
-      <c r="C14" s="107" t="s">
+      <c r="J13" s="78" t="s">
+        <v>5</v>
+      </c>
+      <c r="K13" s="77" t="s">
+        <v>349</v>
+      </c>
+      <c r="L13" s="77" t="s">
+        <v>350</v>
+      </c>
+      <c r="M13" s="77" t="s">
+        <v>351</v>
+      </c>
+      <c r="N13" s="77" t="s">
+        <v>352</v>
+      </c>
+      <c r="O13" s="77" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="14" spans="3:15" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="C14" s="78" t="s">
         <v>293</v>
       </c>
-      <c r="D14" s="106" t="s">
+      <c r="D14" s="77" t="s">
         <v>294</v>
       </c>
-      <c r="E14" s="106" t="s">
+      <c r="E14" s="77" t="s">
         <v>295</v>
       </c>
-      <c r="F14" s="106" t="s">
+      <c r="F14" s="77" t="s">
         <v>296</v>
       </c>
-      <c r="G14" s="106" t="s">
+      <c r="G14" s="77" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="15" spans="3:7" ht="145" x14ac:dyDescent="0.35">
-      <c r="C15" s="107" t="s">
+      <c r="J14" s="78" t="s">
+        <v>5</v>
+      </c>
+      <c r="K14" s="77" t="s">
+        <v>354</v>
+      </c>
+      <c r="L14" s="77" t="s">
+        <v>355</v>
+      </c>
+      <c r="M14" s="77" t="s">
+        <v>356</v>
+      </c>
+      <c r="N14" s="77" t="s">
+        <v>357</v>
+      </c>
+      <c r="O14" s="77" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="15" spans="3:15" ht="145" x14ac:dyDescent="0.35">
+      <c r="C15" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="106" t="s">
+      <c r="D15" s="77" t="s">
         <v>298</v>
       </c>
-      <c r="E15" s="106" t="s">
+      <c r="E15" s="77" t="s">
         <v>299</v>
       </c>
-      <c r="F15" s="106" t="s">
+      <c r="F15" s="77" t="s">
         <v>300</v>
       </c>
-      <c r="G15" s="106" t="s">
+      <c r="G15" s="77" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="16" spans="3:7" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="C16" s="107" t="s">
+      <c r="J15" s="78" t="s">
+        <v>359</v>
+      </c>
+      <c r="K15" s="77" t="s">
+        <v>136</v>
+      </c>
+      <c r="L15" s="77" t="s">
+        <v>360</v>
+      </c>
+      <c r="M15" s="77" t="s">
+        <v>361</v>
+      </c>
+      <c r="N15" s="77" t="s">
+        <v>362</v>
+      </c>
+      <c r="O15" s="77" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="16" spans="3:15" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="C16" s="78" t="s">
         <v>302</v>
       </c>
-      <c r="D16" s="106" t="s">
+      <c r="D16" s="77" t="s">
         <v>303</v>
       </c>
-      <c r="E16" s="106" t="s">
+      <c r="E16" s="77" t="s">
         <v>304</v>
       </c>
-      <c r="F16" s="106" t="s">
+      <c r="F16" s="77" t="s">
         <v>305</v>
       </c>
-      <c r="G16" s="106" t="s">
+      <c r="G16" s="77" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="17" spans="3:7" ht="188.5" x14ac:dyDescent="0.35">
-      <c r="C17" s="107" t="s">
+      <c r="J16" s="78" t="s">
+        <v>359</v>
+      </c>
+      <c r="K16" s="77" t="s">
+        <v>141</v>
+      </c>
+      <c r="L16" s="77" t="s">
+        <v>364</v>
+      </c>
+      <c r="M16" s="77" t="s">
+        <v>365</v>
+      </c>
+      <c r="N16" s="77" t="s">
+        <v>366</v>
+      </c>
+      <c r="O16" s="77" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="17" spans="3:15" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="C17" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="D17" s="106" t="s">
+      <c r="D17" s="77" t="s">
         <v>307</v>
       </c>
-      <c r="E17" s="106" t="s">
+      <c r="E17" s="77" t="s">
         <v>308</v>
       </c>
-      <c r="F17" s="106" t="s">
+      <c r="F17" s="77" t="s">
         <v>309</v>
       </c>
-      <c r="G17" s="106" t="s">
+      <c r="G17" s="77" t="s">
         <v>310</v>
+      </c>
+      <c r="J17" s="78" t="s">
+        <v>359</v>
+      </c>
+      <c r="K17" s="77" t="s">
+        <v>138</v>
+      </c>
+      <c r="L17" s="77" t="s">
+        <v>368</v>
+      </c>
+      <c r="M17" s="77" t="s">
+        <v>369</v>
+      </c>
+      <c r="N17" s="77" t="s">
+        <v>370</v>
+      </c>
+      <c r="O17" s="77" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="J18" s="78" t="s">
+        <v>359</v>
+      </c>
+      <c r="K18" s="77" t="s">
+        <v>372</v>
+      </c>
+      <c r="L18" s="77" t="s">
+        <v>373</v>
+      </c>
+      <c r="M18" s="77" t="s">
+        <v>374</v>
+      </c>
+      <c r="N18" s="77" t="s">
+        <v>375</v>
+      </c>
+      <c r="O18" s="77" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="J19" s="78" t="s">
+        <v>359</v>
+      </c>
+      <c r="K19" s="77" t="s">
+        <v>377</v>
+      </c>
+      <c r="L19" s="77" t="s">
+        <v>378</v>
+      </c>
+      <c r="M19" s="77" t="s">
+        <v>379</v>
+      </c>
+      <c r="N19" s="77" t="s">
+        <v>380</v>
+      </c>
+      <c r="O19" s="77" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="20" spans="3:15" ht="116" x14ac:dyDescent="0.35">
+      <c r="J20" s="78" t="s">
+        <v>359</v>
+      </c>
+      <c r="K20" s="77" t="s">
+        <v>139</v>
+      </c>
+      <c r="L20" s="77" t="s">
+        <v>382</v>
+      </c>
+      <c r="M20" s="77" t="s">
+        <v>383</v>
+      </c>
+      <c r="N20" s="77" t="s">
+        <v>384</v>
+      </c>
+      <c r="O20" s="77" t="s">
+        <v>385</v>
       </c>
     </row>
   </sheetData>
@@ -5093,21 +5630,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006A8CA6F7058DE64A9BC84A9624507C69" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f0fa54b93c06fd173c1bddb4410339ff">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b3c07c23-e01c-4f13-80a8-1ad5b1da3f41" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="20825863041d3ab0d0e3664b835e9e9f" ns2:_="">
     <xsd:import namespace="b3c07c23-e01c-4f13-80a8-1ad5b1da3f41"/>
@@ -5275,31 +5797,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD9C01B8-6567-4906-9D71-77FC831F1D25}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="b3c07c23-e01c-4f13-80a8-1ad5b1da3f41"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A60ECFBE-6E16-4F17-A87D-647817EF59AA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF38ADA5-8CF8-48DC-8FB0-75444658E5E2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5317,6 +5830,30 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A60ECFBE-6E16-4F17-A87D-647817EF59AA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD9C01B8-6567-4906-9D71-77FC831F1D25}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="b3c07c23-e01c-4f13-80a8-1ad5b1da3f41"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{ea60d57e-af5b-4752-ac57-3e4f28ca11dc}" enabled="1" method="Standard" siteId="{36da45f1-dd2c-4d1f-af13-5abe46b99921}" removed="0"/>
